--- a/data/2026_ast_data_amik.xlsx
+++ b/data/2026_ast_data_amik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://outlookuga-my.sharepoint.com/personal/hm64666_uga_edu/Documents/Amik/2026_multidrug_resistance_milk/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="8_{A0616AD4-DA60-2246-804B-4B84A314F82E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F150C95-8BB8-CB4C-A9FE-6C65C0C471D8}"/>
+  <xr:revisionPtr revIDLastSave="116" documentId="8_{A0616AD4-DA60-2246-804B-4B84A314F82E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED3A41A7-456E-1844-97D7-0346625F75D8}"/>
   <bookViews>
     <workbookView xWindow="-38560" yWindow="-28200" windowWidth="34400" windowHeight="26880" xr2:uid="{50F79ADC-DF4E-534A-A665-303288AA0405}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="21">
   <si>
     <t>S. urberis</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>E. coli</t>
+  </si>
+  <si>
+    <t>Enrofloxacin</t>
   </si>
 </sst>
 </file>
@@ -554,7 +557,9 @@
       <c r="L1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="1"/>
+      <c r="M1" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -956,7 +961,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -982,7 +987,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1008,7 +1013,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1034,7 +1039,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1059,8 +1064,11 @@
       <c r="H20" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="M20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1085,8 +1093,11 @@
       <c r="H21" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="M21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1111,8 +1122,11 @@
       <c r="H22" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="M22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1137,8 +1151,11 @@
       <c r="H23" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="M23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1163,8 +1180,11 @@
       <c r="H24" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="M24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1189,8 +1209,11 @@
       <c r="H25" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="M25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1215,8 +1238,11 @@
       <c r="H26" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="M26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1241,8 +1267,11 @@
       <c r="H27" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="M27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1267,8 +1296,11 @@
       <c r="H28" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="M28" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1293,8 +1325,11 @@
       <c r="H29" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="M29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1319,8 +1354,11 @@
       <c r="H30" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="M30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1345,8 +1383,11 @@
       <c r="I31" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="M31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1371,8 +1412,11 @@
       <c r="I32" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M32" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1397,8 +1441,11 @@
       <c r="I33" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M33" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1423,8 +1470,11 @@
       <c r="I34" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M34" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1449,8 +1499,11 @@
       <c r="I35" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M35" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1475,8 +1528,11 @@
       <c r="I36" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M36" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1501,8 +1557,11 @@
       <c r="I37" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M37" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1527,8 +1586,11 @@
       <c r="I38" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M38" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1553,8 +1615,11 @@
       <c r="I39" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M39" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1579,8 +1644,11 @@
       <c r="I40" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M40" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1605,8 +1673,11 @@
       <c r="I41" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1631,8 +1702,11 @@
       <c r="I42" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M42" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1657,8 +1731,11 @@
       <c r="I43" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M43" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1683,8 +1760,11 @@
       <c r="I44" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M44" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1709,8 +1789,11 @@
       <c r="I45" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M45" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1735,8 +1818,11 @@
       <c r="L46" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M46" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1761,8 +1847,11 @@
       <c r="L47" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M47" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1787,8 +1876,11 @@
       <c r="L48" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M48" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1813,8 +1905,11 @@
       <c r="L49" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M49" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1839,8 +1934,11 @@
       <c r="L50" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M50" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1863,6 +1961,9 @@
         <v>9</v>
       </c>
       <c r="L51" t="s">
+        <v>9</v>
+      </c>
+      <c r="M51" t="s">
         <v>9</v>
       </c>
     </row>
